--- a/academias/Cultura Digital - Estadisticos 20241.xlsx
+++ b/academias/Cultura Digital - Estadisticos 20241.xlsx
@@ -1118,25 +1118,25 @@
         <v>48</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F4">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1">
-        <v>0</v>
+        <v>79.2</v>
       </c>
       <c r="H4" s="1">
-        <v>100</v>
+        <v>20.8</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="J4">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K4" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1255,25 +1255,25 @@
         <v>235</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="F8">
-        <v>235</v>
+        <v>197</v>
       </c>
       <c r="G8" s="1">
-        <v>0</v>
+        <v>16.2</v>
       </c>
       <c r="H8" s="1">
-        <v>100</v>
+        <v>83.8</v>
       </c>
       <c r="I8" s="2">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="J8">
-        <v>235</v>
+        <v>187</v>
       </c>
       <c r="K8" s="1">
-        <v>100</v>
+        <v>79.59999999999999</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1290,25 +1290,25 @@
         <v>40</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>40</v>
+        <v>9</v>
       </c>
       <c r="G9" s="1">
-        <v>0</v>
+        <v>77.5</v>
       </c>
       <c r="H9" s="1">
-        <v>100</v>
+        <v>22.5</v>
       </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="J9">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K9" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1325,25 +1325,25 @@
         <v>34</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F10">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1">
-        <v>0</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>100</v>
+        <v>17.6</v>
       </c>
       <c r="I10" s="2">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="J10">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K10" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1360,25 +1360,25 @@
         <v>33</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F11">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="G11" s="1">
-        <v>0</v>
+        <v>78.8</v>
       </c>
       <c r="H11" s="1">
-        <v>100</v>
+        <v>21.2</v>
       </c>
       <c r="I11" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J11">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K11" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1395,25 +1395,25 @@
         <v>23</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F12">
-        <v>23</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>0</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>100</v>
+        <v>17.4</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J12">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="K12" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1430,25 +1430,25 @@
         <v>19</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="F13">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G13" s="1">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="J13">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="K13" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1462,25 +1462,25 @@
         <v>149</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="F14">
-        <v>149</v>
+        <v>26</v>
       </c>
       <c r="G14" s="1">
-        <v>0</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>100</v>
+        <v>17.4</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="J14">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="K14" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1491,25 +1491,25 @@
         <v>384</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>161</v>
       </c>
       <c r="F15">
-        <v>384</v>
+        <v>223</v>
       </c>
       <c r="G15" s="1">
-        <v>0</v>
+        <v>41.9</v>
       </c>
       <c r="H15" s="1">
-        <v>100</v>
+        <v>58.1</v>
       </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="J15">
-        <v>384</v>
+        <v>187</v>
       </c>
       <c r="K15" s="1">
-        <v>100</v>
+        <v>48.7</v>
       </c>
     </row>
   </sheetData>
@@ -1647,19 +1647,19 @@
         <v>48</v>
       </c>
       <c r="E4">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="F4">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G4" s="1">
-        <v>70.8</v>
+        <v>79.2</v>
       </c>
       <c r="H4" s="1">
-        <v>29.2</v>
+        <v>20.8</v>
       </c>
       <c r="I4" s="2">
-        <v>6.1</v>
+        <v>6.9</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1784,19 +1784,19 @@
         <v>235</v>
       </c>
       <c r="E8">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="F8">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="G8" s="1">
-        <v>74</v>
+        <v>75.7</v>
       </c>
       <c r="H8" s="1">
-        <v>26</v>
+        <v>24.3</v>
       </c>
       <c r="I8" s="2">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -1819,19 +1819,19 @@
         <v>40</v>
       </c>
       <c r="E9">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="F9">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="G9" s="1">
-        <v>62.5</v>
+        <v>77.5</v>
       </c>
       <c r="H9" s="1">
-        <v>37.5</v>
+        <v>22.5</v>
       </c>
       <c r="I9" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -1854,16 +1854,16 @@
         <v>34</v>
       </c>
       <c r="E10">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F10">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1">
-        <v>73.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="H10" s="1">
-        <v>26.5</v>
+        <v>17.6</v>
       </c>
       <c r="I10" s="2">
         <v>7.4</v>
@@ -1889,19 +1889,19 @@
         <v>33</v>
       </c>
       <c r="E11">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G11" s="1">
-        <v>69.7</v>
+        <v>78.8</v>
       </c>
       <c r="H11" s="1">
-        <v>30.3</v>
+        <v>21.2</v>
       </c>
       <c r="I11" s="2">
-        <v>6.7</v>
+        <v>6.9</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -1924,19 +1924,19 @@
         <v>23</v>
       </c>
       <c r="E12">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F12">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G12" s="1">
-        <v>78.3</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H12" s="1">
-        <v>21.7</v>
+        <v>17.4</v>
       </c>
       <c r="I12" s="2">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1971,7 +1971,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1991,19 +1991,19 @@
         <v>149</v>
       </c>
       <c r="E14">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="F14">
-        <v>39</v>
+        <v>26</v>
       </c>
       <c r="G14" s="1">
-        <v>73.8</v>
+        <v>82.59999999999999</v>
       </c>
       <c r="H14" s="1">
-        <v>26.2</v>
+        <v>17.4</v>
       </c>
       <c r="I14" s="2">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2020,19 +2020,19 @@
         <v>384</v>
       </c>
       <c r="E15">
-        <v>284</v>
+        <v>301</v>
       </c>
       <c r="F15">
-        <v>100</v>
+        <v>83</v>
       </c>
       <c r="G15" s="1">
-        <v>74</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>26</v>
+        <v>21.6</v>
       </c>
       <c r="I15" s="2">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="J15">
         <v>0</v>

--- a/academias/Cultura Digital - Estadisticos 20241.xlsx
+++ b/academias/Cultura Digital - Estadisticos 20241.xlsx
@@ -1048,25 +1048,25 @@
         <v>40</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="F2">
-        <v>40</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1">
-        <v>0</v>
+        <v>82.5</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>17.5</v>
       </c>
       <c r="I2" s="2">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="J2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1083,25 +1083,25 @@
         <v>41</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F3">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="G3" s="1">
-        <v>0</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>100</v>
+        <v>24.4</v>
       </c>
       <c r="I3" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="K3" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1153,25 +1153,25 @@
         <v>36</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F5">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="G5" s="1">
-        <v>0</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="H5" s="1">
-        <v>100</v>
+        <v>19.4</v>
       </c>
       <c r="I5" s="2">
-        <v>0</v>
+        <v>6.7</v>
       </c>
       <c r="J5">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="K5" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1188,25 +1188,25 @@
         <v>37</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F6">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="G6" s="1">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>6.9</v>
       </c>
       <c r="J6">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="K6" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1223,25 +1223,25 @@
         <v>33</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="F7">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="G7" s="1">
-        <v>0</v>
+        <v>78.8</v>
       </c>
       <c r="H7" s="1">
-        <v>100</v>
+        <v>21.2</v>
       </c>
       <c r="I7" s="2">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="J7">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K7" s="1">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1255,25 +1255,25 @@
         <v>235</v>
       </c>
       <c r="E8">
-        <v>38</v>
+        <v>184</v>
       </c>
       <c r="F8">
-        <v>197</v>
+        <v>51</v>
       </c>
       <c r="G8" s="1">
-        <v>16.2</v>
+        <v>78.3</v>
       </c>
       <c r="H8" s="1">
-        <v>83.8</v>
+        <v>21.7</v>
       </c>
       <c r="I8" s="2">
-        <v>1.2</v>
+        <v>7.1</v>
       </c>
       <c r="J8">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="K8" s="1">
-        <v>79.59999999999999</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1491,25 +1491,25 @@
         <v>384</v>
       </c>
       <c r="E15">
-        <v>161</v>
+        <v>307</v>
       </c>
       <c r="F15">
-        <v>223</v>
+        <v>77</v>
       </c>
       <c r="G15" s="1">
-        <v>41.9</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>58.1</v>
+        <v>20.1</v>
       </c>
       <c r="I15" s="2">
-        <v>3.9</v>
+        <v>7.1</v>
       </c>
       <c r="J15">
-        <v>187</v>
+        <v>0</v>
       </c>
       <c r="K15" s="1">
-        <v>48.7</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1577,19 +1577,19 @@
         <v>40</v>
       </c>
       <c r="E2">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G2" s="1">
-        <v>77.5</v>
+        <v>82.5</v>
       </c>
       <c r="H2" s="1">
-        <v>22.5</v>
+        <v>17.5</v>
       </c>
       <c r="I2" s="2">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1612,19 +1612,19 @@
         <v>41</v>
       </c>
       <c r="E3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F3">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3" s="1">
-        <v>70.7</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="H3" s="1">
-        <v>29.3</v>
+        <v>24.4</v>
       </c>
       <c r="I3" s="2">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1694,7 +1694,7 @@
         <v>19.4</v>
       </c>
       <c r="I5" s="2">
-        <v>6.3</v>
+        <v>6.6</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1717,19 +1717,19 @@
         <v>37</v>
       </c>
       <c r="E6">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G6" s="1">
-        <v>75.7</v>
+        <v>73</v>
       </c>
       <c r="H6" s="1">
-        <v>24.3</v>
+        <v>27</v>
       </c>
       <c r="I6" s="2">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1752,19 +1752,19 @@
         <v>33</v>
       </c>
       <c r="E7">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F7">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G7" s="1">
-        <v>69.7</v>
+        <v>78.8</v>
       </c>
       <c r="H7" s="1">
-        <v>30.3</v>
+        <v>21.2</v>
       </c>
       <c r="I7" s="2">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1784,19 +1784,19 @@
         <v>235</v>
       </c>
       <c r="E8">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="F8">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G8" s="1">
-        <v>75.7</v>
+        <v>78.3</v>
       </c>
       <c r="H8" s="1">
-        <v>24.3</v>
+        <v>21.7</v>
       </c>
       <c r="I8" s="2">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2020,19 +2020,19 @@
         <v>384</v>
       </c>
       <c r="E15">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="F15">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="G15" s="1">
-        <v>78.40000000000001</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>21.6</v>
+        <v>20.1</v>
       </c>
       <c r="I15" s="2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J15">
         <v>0</v>

--- a/academias/Cultura Digital - Estadisticos 20241.xlsx
+++ b/academias/Cultura Digital - Estadisticos 20241.xlsx
@@ -1819,16 +1819,16 @@
         <v>40</v>
       </c>
       <c r="E9">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F9">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>77.5</v>
+        <v>97.5</v>
       </c>
       <c r="H9" s="1">
-        <v>22.5</v>
+        <v>2.5</v>
       </c>
       <c r="I9" s="2">
         <v>6.8</v>
@@ -1854,19 +1854,19 @@
         <v>34</v>
       </c>
       <c r="E10">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="F10">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G10" s="1">
-        <v>82.40000000000001</v>
+        <v>91.2</v>
       </c>
       <c r="H10" s="1">
-        <v>17.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I10" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J10">
         <v>0</v>
@@ -1889,16 +1889,16 @@
         <v>33</v>
       </c>
       <c r="E11">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F11">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G11" s="1">
-        <v>78.8</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="H11" s="1">
-        <v>21.2</v>
+        <v>9.1</v>
       </c>
       <c r="I11" s="2">
         <v>6.9</v>
@@ -1924,19 +1924,19 @@
         <v>23</v>
       </c>
       <c r="E12">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F12">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
-        <v>82.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H12" s="1">
-        <v>17.4</v>
+        <v>0</v>
       </c>
       <c r="I12" s="2">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="J12">
         <v>0</v>
@@ -1971,7 +1971,7 @@
         <v>0</v>
       </c>
       <c r="I13" s="2">
-        <v>8.6</v>
+        <v>8.1</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1991,19 +1991,19 @@
         <v>149</v>
       </c>
       <c r="E14">
-        <v>123</v>
+        <v>142</v>
       </c>
       <c r="F14">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="G14" s="1">
-        <v>82.59999999999999</v>
+        <v>95.3</v>
       </c>
       <c r="H14" s="1">
-        <v>17.4</v>
+        <v>4.7</v>
       </c>
       <c r="I14" s="2">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="J14">
         <v>0</v>
@@ -2020,16 +2020,16 @@
         <v>384</v>
       </c>
       <c r="E15">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="F15">
-        <v>77</v>
+        <v>58</v>
       </c>
       <c r="G15" s="1">
-        <v>79.90000000000001</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>20.1</v>
+        <v>15.1</v>
       </c>
       <c r="I15" s="2">
         <v>7</v>

--- a/academias/Cultura Digital - Estadisticos 20241.xlsx
+++ b/academias/Cultura Digital - Estadisticos 20241.xlsx
@@ -1577,19 +1577,19 @@
         <v>40</v>
       </c>
       <c r="E2">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G2" s="1">
-        <v>82.5</v>
+        <v>97.5</v>
       </c>
       <c r="H2" s="1">
-        <v>17.5</v>
+        <v>2.5</v>
       </c>
       <c r="I2" s="2">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="J2">
         <v>0</v>
@@ -1612,19 +1612,19 @@
         <v>41</v>
       </c>
       <c r="E3">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F3">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="G3" s="1">
-        <v>75.59999999999999</v>
+        <v>92.7</v>
       </c>
       <c r="H3" s="1">
-        <v>24.4</v>
+        <v>7.3</v>
       </c>
       <c r="I3" s="2">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1647,19 +1647,19 @@
         <v>48</v>
       </c>
       <c r="E4">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="F4">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G4" s="1">
-        <v>79.2</v>
+        <v>100</v>
       </c>
       <c r="H4" s="1">
-        <v>20.8</v>
+        <v>0</v>
       </c>
       <c r="I4" s="2">
-        <v>6.9</v>
+        <v>7.1</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1682,19 +1682,19 @@
         <v>36</v>
       </c>
       <c r="E5">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" s="1">
+        <v>97.2</v>
+      </c>
+      <c r="H5" s="1">
+        <v>2.8</v>
+      </c>
+      <c r="I5" s="2">
         <v>7</v>
-      </c>
-      <c r="G5" s="1">
-        <v>80.59999999999999</v>
-      </c>
-      <c r="H5" s="1">
-        <v>19.4</v>
-      </c>
-      <c r="I5" s="2">
-        <v>6.6</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1717,19 +1717,19 @@
         <v>37</v>
       </c>
       <c r="E6">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="F6">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>73</v>
+        <v>97.3</v>
       </c>
       <c r="H6" s="1">
-        <v>27</v>
+        <v>2.7</v>
       </c>
       <c r="I6" s="2">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="J6">
         <v>0</v>
@@ -1752,19 +1752,19 @@
         <v>33</v>
       </c>
       <c r="E7">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="F7">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>78.8</v>
+        <v>97</v>
       </c>
       <c r="H7" s="1">
-        <v>21.2</v>
+        <v>3</v>
       </c>
       <c r="I7" s="2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -1784,19 +1784,19 @@
         <v>235</v>
       </c>
       <c r="E8">
-        <v>184</v>
+        <v>228</v>
       </c>
       <c r="F8">
-        <v>51</v>
+        <v>7</v>
       </c>
       <c r="G8" s="1">
-        <v>78.3</v>
+        <v>97</v>
       </c>
       <c r="H8" s="1">
-        <v>21.7</v>
+        <v>3</v>
       </c>
       <c r="I8" s="2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J8">
         <v>0</v>
@@ -2020,19 +2020,19 @@
         <v>384</v>
       </c>
       <c r="E15">
-        <v>326</v>
+        <v>370</v>
       </c>
       <c r="F15">
-        <v>58</v>
+        <v>14</v>
       </c>
       <c r="G15" s="1">
-        <v>84.90000000000001</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="H15" s="1">
-        <v>15.1</v>
+        <v>3.6</v>
       </c>
       <c r="I15" s="2">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="J15">
         <v>0</v>
